--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-functional-CYC-3/03-test-cases/CYC-3-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-functional-CYC-3/03-test-cases/CYC-3-test-cases.xlsx
@@ -3635,7 +3635,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-11T16:16:08.013Z</t>
+    <t>2026-10-11T16:44:58.647Z</t>
   </si>
   <si>
     <t>Column order</t>
@@ -4867,7 +4867,7 @@
         <v>122</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>23</v>
@@ -4914,7 +4914,7 @@
         <v>129</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>23</v>
@@ -4961,7 +4961,7 @@
         <v>134</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>23</v>
@@ -5008,7 +5008,7 @@
         <v>139</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>23</v>
@@ -6559,7 +6559,7 @@
         <v>317</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>23</v>
@@ -6606,7 +6606,7 @@
         <v>322</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>23</v>
@@ -6653,7 +6653,7 @@
         <v>327</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>23</v>
@@ -6700,7 +6700,7 @@
         <v>332</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>23</v>
@@ -7546,7 +7546,7 @@
         <v>439</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>23</v>
@@ -7593,7 +7593,7 @@
         <v>444</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>23</v>
@@ -7640,7 +7640,7 @@
         <v>449</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>23</v>
@@ -7687,7 +7687,7 @@
         <v>454</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="I77" s="3" t="s">
         <v>23</v>
@@ -9238,7 +9238,7 @@
         <v>625</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>23</v>
@@ -9285,7 +9285,7 @@
         <v>625</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>23</v>
@@ -9332,7 +9332,7 @@
         <v>635</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>23</v>
@@ -9567,7 +9567,7 @@
         <v>641</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>23</v>
@@ -9614,7 +9614,7 @@
         <v>673</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="I118" s="3" t="s">
         <v>23</v>
@@ -9661,7 +9661,7 @@
         <v>679</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="I119" s="3" t="s">
         <v>23</v>
@@ -9708,7 +9708,7 @@
         <v>685</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="I120" s="3" t="s">
         <v>23</v>
@@ -9755,7 +9755,7 @@
         <v>641</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="I121" s="3" t="s">
         <v>23</v>
@@ -9802,7 +9802,7 @@
         <v>697</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="I122" s="3" t="s">
         <v>23</v>
@@ -10413,7 +10413,7 @@
         <v>773</v>
       </c>
       <c r="H135" s="5" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="I135" s="5" t="s">
         <v>23</v>
@@ -10460,7 +10460,7 @@
         <v>779</v>
       </c>
       <c r="H136" s="5" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="I136" s="5" t="s">
         <v>23</v>
@@ -10507,7 +10507,7 @@
         <v>785</v>
       </c>
       <c r="H137" s="5" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="I137" s="5" t="s">
         <v>23</v>
@@ -10554,7 +10554,7 @@
         <v>789</v>
       </c>
       <c r="H138" s="5" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="I138" s="5" t="s">
         <v>23</v>
@@ -10601,7 +10601,7 @@
         <v>795</v>
       </c>
       <c r="H139" s="5" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="I139" s="5" t="s">
         <v>23</v>
@@ -10648,7 +10648,7 @@
         <v>800</v>
       </c>
       <c r="H140" s="5" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="I140" s="5" t="s">
         <v>23</v>
@@ -10695,7 +10695,7 @@
         <v>806</v>
       </c>
       <c r="H141" s="5" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="I141" s="5" t="s">
         <v>23</v>
@@ -10742,7 +10742,7 @@
         <v>812</v>
       </c>
       <c r="H142" s="5" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="I142" s="5" t="s">
         <v>23</v>
@@ -10789,7 +10789,7 @@
         <v>818</v>
       </c>
       <c r="H143" s="5" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="I143" s="5" t="s">
         <v>23</v>
@@ -10836,7 +10836,7 @@
         <v>823</v>
       </c>
       <c r="H144" s="5" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="I144" s="5" t="s">
         <v>23</v>
@@ -10883,7 +10883,7 @@
         <v>829</v>
       </c>
       <c r="H145" s="5" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="I145" s="5" t="s">
         <v>23</v>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-functional-CYC-3/03-test-cases/CYC-3-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-functional-CYC-3/03-test-cases/CYC-3-test-cases.xlsx
@@ -3635,7 +3635,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-11T16:44:58.647Z</t>
+    <t>2026-10-11T17:07:27.935Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-functional-CYC-3/03-test-cases/CYC-3-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-functional-CYC-3/03-test-cases/CYC-3-test-cases.xlsx
@@ -3635,7 +3635,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-11T17:07:27.935Z</t>
+    <t>2026-10-12T01:35:49.484Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-functional-CYC-3/03-test-cases/CYC-3-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-functional-CYC-3/03-test-cases/CYC-3-test-cases.xlsx
@@ -1911,7 +1911,7 @@
     <t>Verify a change above 1% needs acknowledgement before checkout.</t>
   </si>
   <si>
-    <t>The six hotel services are running with their seeded catalogue (reset before the case). The nightly rate rises 30% after the cart is created.</t>
+    <t>The six hotel services are running with their seeded catalogue (reset before the case). The nightly rate is 200 when the cart is created and rises 30% to 260.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Create a cart
@@ -1937,7 +1937,7 @@
     <t>Verify a change within 1% is applied without blocking the guest.</t>
   </si>
   <si>
-    <t>The six hotel services are running with their seeded catalogue (reset before the case). The nightly rate rises 0.5% after the cart is created.</t>
+    <t>The six hotel services are running with their seeded catalogue (reset before the case). The nightly rate is 200 when the cart is created and rises 0.5% to 201.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Create a cart
@@ -3635,7 +3635,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-12T01:35:49.484Z</t>
+    <t>2026-10-12T02:10:48.946Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-functional-CYC-3/03-test-cases/CYC-3-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-functional-CYC-3/03-test-cases/CYC-3-test-cases.xlsx
@@ -3635,7 +3635,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-12T02:10:48.946Z</t>
+    <t>2026-10-12T02:22:46.839Z</t>
   </si>
   <si>
     <t>Column order</t>
